--- a/Дневники/Дневник Филатов.xlsx
+++ b/Дневники/Дневник Филатов.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\УП.02.01 Ролевая игра Проектная группа\Материалы\!Общее\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\УП.02.01 Ролевая игра Проектная группа\Отчет Дневники\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40615BC-1446-4C89-A95C-61F55494C7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A018CFC-955B-4499-9FDE-294999F20DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6765" yWindow="4665" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Дата1" sheetId="5" r:id="rId1"/>
@@ -18,17 +18,26 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Дата1!$B$3:$D$3</definedName>
   </definedNames>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Задача</t>
   </si>
@@ -55,6 +64,18 @@
   </si>
   <si>
     <t>Доработка логики приложения</t>
+  </si>
+  <si>
+    <t>День 1</t>
+  </si>
+  <si>
+    <t>День 2</t>
+  </si>
+  <si>
+    <t>День 3</t>
+  </si>
+  <si>
+    <t>День 5</t>
   </si>
 </sst>
 </file>
@@ -99,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -168,11 +189,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -180,18 +210,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="21" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -199,6 +226,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -492,11 +528,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
@@ -509,301 +545,310 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="5">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+    </row>
+    <row r="6" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="3">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D6" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="93.75" x14ac:dyDescent="0.3">
-      <c r="B5" s="5">
+    <row r="7" spans="2:4" ht="93.75" x14ac:dyDescent="0.3">
+      <c r="B7" s="3">
         <v>0.36458333333333331</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D7" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="5">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="B9" s="3">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D9" s="3">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="75" x14ac:dyDescent="0.3">
-      <c r="B8" s="5">
+    <row r="10" spans="2:4" ht="75" x14ac:dyDescent="0.3">
+      <c r="B10" s="3">
         <v>0.34375</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D10" s="3">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="5">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="B12" s="3">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D12" s="3">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="56.25" x14ac:dyDescent="0.3">
-      <c r="B11" s="5">
+    <row r="13" spans="2:4" ht="56.25" x14ac:dyDescent="0.3">
+      <c r="B13" s="3">
         <v>0.34375</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D13" s="3">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="5">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D15" s="3">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="5">
+    <row r="16" spans="2:4" ht="37.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
         <v>0.34375</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D16" s="3">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:D3" xr:uid="{942723FC-F17B-4EAF-B780-F95BEB36B17D}"/>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B4:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
